--- a/output/pdf_financials_xlsx/MCT.P.xlsx
+++ b/output/pdf_financials_xlsx/MCT.P.xlsx
@@ -1916,19 +1916,17 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0.020307</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.002461</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.041973</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.011921</v>
       </c>
     </row>
     <row r="65">
@@ -1979,19 +1977,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.008</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.013622</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="68">
@@ -2697,13 +2693,13 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004713</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001309</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000885</v>
       </c>
     </row>
     <row r="102">
@@ -2792,13 +2788,13 @@
         <v>0.042432</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.015346</v>
+        <v>-0.020059</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.042634</v>
+        <v>0.041325</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.032474</v>
+        <v>-0.033359</v>
       </c>
     </row>
     <row r="107">
@@ -5914,7 +5910,11 @@
           <t>GST Receivable</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
